--- a/Data/Metadata/PlanEdits/TableMigrationReport-Dec-1.xlsx
+++ b/Data/Metadata/PlanEdits/TableMigrationReport-Dec-1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SRC\ASP.net\TrackerSQL\Data\Metadata\PlanEdits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE5AE40-9845-4B75-826B-736AB840AD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5A0981-5840-48AF-BA44-D869C6F93444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="23520" xr2:uid="{098D3839-B3D8-48A5-9192-AFFB9CD96D09}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6026" uniqueCount="491">
   <si>
     <t>Table Migration report: 16 Oct 2025</t>
   </si>
@@ -20866,6 +20866,9 @@
       <c r="P560" t="s">
         <v>457</v>
       </c>
+      <c r="Q560" t="s">
+        <v>37</v>
+      </c>
       <c r="R560" t="s">
         <v>39</v>
       </c>
@@ -21596,6 +21599,9 @@
       </c>
       <c r="P579" t="s">
         <v>390</v>
+      </c>
+      <c r="Q579" t="s">
+        <v>37</v>
       </c>
       <c r="R579" t="s">
         <v>39</v>
